--- a/EKG_Kalite_Yönetim_Sistemi/04_Parça ve Proses Kontrolü/02_PPC2 - MSA, Kalibrasyon ve SPC/EKG-KLT-FRM-29_cam_hatti_olcum_sistemleri_analizi_formlari__msa.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/04_Parça ve Proses Kontrolü/02_PPC2 - MSA, Kalibrasyon ve SPC/EKG-KLT-FRM-29_cam_hatti_olcum_sistemleri_analizi_formlari__msa.xlsx
@@ -1780,7 +1780,8 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-FRM-29&amp;C&amp;"Arial,Regular"&amp;11Cam Hattı Ölçüm Sistemleri Analizi Formları - MSA</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 10.06.2026 | Revizyon: 18.09.2026
+Revizyon nedeni: R&amp;&amp;R, nitel uyum ve yanlış kabul/ret formülleri kuruldu; sabit uygunluk kararı kaldırıldı.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -2376,7 +2377,8 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-FRM-29&amp;C&amp;"Arial,Regular"&amp;11Cam Hattı Ölçüm Sistemleri Analizi Formları - MSA</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 10.06.2026 | Revizyon: 18.09.2026
+Revizyon nedeni: R&amp;&amp;R, nitel uyum ve yanlış kabul/ret formülleri kuruldu; sabit uygunluk kararı kaldırıldı.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>